--- a/ig/TEST-SUPPLEMENT/CodeSystem-ParticipationFunction-supplement-fr.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-ParticipationFunction-supplement-fr.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/example/CodeSystem/ParticipationFunction-supplement-fr</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/participationFunction-supplement-fr</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/TEST-SUPPLEMENT/CodeSystem-ParticipationFunction-supplement-fr.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-ParticipationFunction-supplement-fr.xlsx
@@ -72,7 +72,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Traduction Francaise</t>
+    <t>Traduction Française</t>
   </si>
   <si>
     <t>Purpose</t>
